--- a/output/laminas_comunales/comunal_o_ocup_a_2019_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2019_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>47.9155578613281</v>
+        <v>62.5336799621582</v>
       </c>
     </row>
     <row r="3">
@@ -399,7 +399,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>45.403263092041</v>
+        <v>62.470085144043</v>
       </c>
     </row>
     <row r="4">
@@ -414,52 +414,697 @@
         </is>
       </c>
       <c r="C4">
-        <v>44.8667869567871</v>
+        <v>62.2838668823242</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="C5">
-        <v>39.842643737793</v>
+        <v>61.7200241088867</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tocopilla</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="C6">
-        <v>36.5330200195312</v>
+        <v>59.0146484375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>56.4917449951172</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>55.9985771179199</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>55.5906867980957</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>55.3463325500488</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>54.9160919189453</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>54.8585472106934</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>54.8007965087891</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>54.1163368225098</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>2104</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Taltal</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C15">
+        <v>52.8158302307129</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>51.2622909545898</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>48.3554954528809</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>47.9155578613281</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>46.4504585266113</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>45.403263092041</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>45.1115341186523</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>44.8667869567871</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>44.4951627404426</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>44.2962951660156</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>42.4675559997559</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>42.2162818908691</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>40.8135185241699</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>39.842643737793</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>39.1933212280273</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>37.7187957763672</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>36.5330200195312</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>36.2778205871582</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>36.2300224304199</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>36.0449180603027</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C35">
         <v>35.2765007019043</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>35.1563758850098</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>34.5170707702637</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>34.4034729003906</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>34.3912353515625</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>31.5724601745605</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>28.0718288421631</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>25.6366577148438</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>25.1948184967041</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>20.114595413208</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>14.7173357009888</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>14.6154594421387</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>14.5618143081665</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>12.3894157409668</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>11.4408674240112</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>7.33652305603027</v>
       </c>
     </row>
   </sheetData>
